--- a/forms/trg/Formulir_TRG_msbd.xlsx
+++ b/forms/trg/Formulir_TRG_msbd.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. Anas Iswanto Anwar, SE., MA., CWM., CRBC.</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -951,7 +955,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -988,7 +992,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1025,7 +1029,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1054,7 +1058,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1087,7 +1091,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1120,7 +1124,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -1149,7 +1153,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1182,7 +1186,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1219,7 +1223,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1256,7 +1260,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1297,7 +1301,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1334,7 +1338,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1371,7 +1375,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1404,7 +1408,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1441,7 +1445,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1449,7 +1453,11 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E20" s="11" t="n"/>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Welcome to the Microfinance and Small Business Development Research Group. We research and develop microfinance solutions to empower low-income households and small businesses by providing access to financial services. Our work focuses on sustainable economic growth, financial inclusion, and poverty alleviation through innovative lending, savings, and financial support systems. Join us in advancing microfinance initiatives that foster entrepreneurship and economic resilience across communities worldwide</t>
+        </is>
+      </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
